--- a/school_registration_forms/025_school_trip_consent_form--school_registration_forms.xlsx
+++ b/school_registration_forms/025_school_trip_consent_form--school_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'name':_'consent1',_'label':_'i_agree_to_my_child_attending_the_school_trip'}</t>
+          <t>i_agree_to_my_child_attending_the_school_trip</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'name': 'consent1', 'label': 'I agree to my child attending the school trip'}</t>
+          <t>I agree to my child attending the school trip</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'name':_'consent2',_'label':_'i_agree_to_the_school_trip_being_held_on_the_specified_date'}</t>
+          <t>i_agree_to_the_school_trip_being_held_on_the_specified_date</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'name': 'consent2', 'label': 'I agree to the school trip being held on the specified date'}</t>
+          <t>I agree to the school trip being held on the specified date</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'name':_'consent3',_'label':_'i_agree_to_my_child_attending_the_trip_without_parental_accompaniment'}</t>
+          <t>i_agree_to_my_child_attending_the_trip_without_parental_accompaniment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'name': 'consent3', 'label': 'I agree to my child attending the trip without parental accompaniment'}</t>
+          <t>I agree to my child attending the trip without parental accompaniment</t>
         </is>
       </c>
     </row>
